--- a/prix/bicones.xlsx
+++ b/prix/bicones.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\raccords-plomberie\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515D4043-3122-4AC1-9FC5-60875E8F773E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1754BDBF-7091-4BEC-B8E2-B10CE5A58E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{CE534A2A-185F-4964-A8EA-80A75C3E7C34}"/>
   </bookViews>
@@ -691,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -729,12 +729,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1120,13 +1114,13 @@
       <c r="C2" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="2">
         <v>4.92</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="3">
         <v>19</v>
       </c>
     </row>
@@ -1140,13 +1134,13 @@
       <c r="C3" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="2">
         <v>5.3100000000000005</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1160,13 +1154,13 @@
       <c r="C4" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="2">
         <v>4.8600000000000003</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1180,13 +1174,13 @@
       <c r="C5" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="2">
         <v>4.8899999999999997</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1200,14 +1194,14 @@
       <c r="C6" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="2">
         <v>5.03</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="15">
-        <v>10</v>
+      <c r="F6" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,13 +1214,13 @@
       <c r="C7" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="2">
         <v>7.82</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="3">
         <v>8</v>
       </c>
     </row>
@@ -1240,13 +1234,13 @@
       <c r="C8" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="2">
         <v>8.17</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="3">
         <v>10</v>
       </c>
     </row>
@@ -1260,13 +1254,13 @@
       <c r="C9" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="2">
         <v>13.1</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="3">
         <v>12</v>
       </c>
     </row>
@@ -1280,13 +1274,13 @@
       <c r="C10" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="2">
         <v>6.49</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1300,13 +1294,13 @@
       <c r="C11" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="2">
         <v>4.8600000000000003</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="3">
         <v>25</v>
       </c>
     </row>
@@ -1320,13 +1314,13 @@
       <c r="C12" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="2">
         <v>6.28</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="3">
         <v>8</v>
       </c>
     </row>
@@ -1340,13 +1334,13 @@
       <c r="C13" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="2">
         <v>3.11</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="3">
         <v>10</v>
       </c>
     </row>
@@ -1360,13 +1354,13 @@
       <c r="C14" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="2">
         <v>4.62</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1380,13 +1374,13 @@
       <c r="C15" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="2">
         <v>4.62</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="3">
         <v>12</v>
       </c>
     </row>
@@ -1400,13 +1394,13 @@
       <c r="C16" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="2">
         <v>13.25</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="3">
         <v>8</v>
       </c>
     </row>
@@ -1420,14 +1414,14 @@
       <c r="C17" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="2">
         <v>5.45</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="15">
-        <v>12</v>
+      <c r="F17" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1440,13 +1434,13 @@
       <c r="C18" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="2">
         <v>6.3</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1460,13 +1454,13 @@
       <c r="C19" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="2">
         <v>8.25</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="3">
         <v>10</v>
       </c>
     </row>
@@ -1480,13 +1474,13 @@
       <c r="C20" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="2">
         <v>11.700000000000001</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1500,13 +1494,13 @@
       <c r="C21" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="2">
         <v>7.18</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1520,13 +1514,13 @@
       <c r="C22" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="2">
         <v>5.9</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1540,13 +1534,13 @@
       <c r="C23" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="2">
         <v>6.99</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="3">
         <v>6</v>
       </c>
     </row>
@@ -1560,13 +1554,13 @@
       <c r="C24" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="2">
         <v>7.68</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="3">
         <v>2</v>
       </c>
     </row>
@@ -1580,13 +1574,13 @@
       <c r="C25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D25" s="14">
-        <v>7.38</v>
+      <c r="D25" s="2">
+        <v>7.7700000000000005</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1600,13 +1594,13 @@
       <c r="C26" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="2">
         <v>12.5</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1620,13 +1614,13 @@
       <c r="C27" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D27" s="14">
-        <v>9.56</v>
+      <c r="D27" s="2">
+        <v>13.700000000000001</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="3">
         <v>17</v>
       </c>
     </row>
@@ -1640,13 +1634,13 @@
       <c r="C28" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="2">
         <v>24.27</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1660,13 +1654,13 @@
       <c r="C29" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="2">
         <v>9.0500000000000007</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="3">
         <v>15</v>
       </c>
     </row>
@@ -1680,13 +1674,13 @@
       <c r="C30" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="2">
         <v>6.63</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1700,13 +1694,13 @@
       <c r="C31" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="2">
         <v>4.16</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1720,13 +1714,13 @@
       <c r="C32" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="2">
         <v>5.01</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1740,14 +1734,14 @@
       <c r="C33" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="2">
         <v>6.3500000000000005</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="15">
-        <v>14</v>
+      <c r="F33" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1760,13 +1754,13 @@
       <c r="C34" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="2">
         <v>7.3500000000000005</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="3">
         <v>9</v>
       </c>
     </row>
@@ -1780,13 +1774,13 @@
       <c r="C35" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="2">
         <v>6.12</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1800,13 +1794,13 @@
       <c r="C36" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="2">
         <v>6.36</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="3">
         <v>9</v>
       </c>
     </row>
@@ -1820,13 +1814,13 @@
       <c r="C37" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="2">
         <v>4.62</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="3">
         <v>14</v>
       </c>
     </row>
@@ -1840,14 +1834,14 @@
       <c r="C38" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="2">
         <v>5.4</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="15">
-        <v>10</v>
+      <c r="F38" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1860,13 +1854,13 @@
       <c r="C39" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="2">
         <v>6.12</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1880,13 +1874,13 @@
       <c r="C40" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="2">
         <v>6.12</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1900,13 +1894,13 @@
       <c r="C41" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D41" s="2">
         <v>10.07</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="3">
         <v>25</v>
       </c>
     </row>
@@ -1920,13 +1914,13 @@
       <c r="C42" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="2">
         <v>4.6000000000000005</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1940,13 +1934,13 @@
       <c r="C43" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D43" s="14">
+      <c r="D43" s="2">
         <v>3.94</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1960,13 +1954,13 @@
       <c r="C44" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="2">
         <v>4.28</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F44" s="15">
+      <c r="F44" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1980,13 +1974,13 @@
       <c r="C45" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D45" s="14">
+      <c r="D45" s="2">
         <v>4.6000000000000005</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="15">
+      <c r="F45" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2000,13 +1994,13 @@
       <c r="C46" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="2">
         <v>5.3</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="15">
+      <c r="F46" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2020,13 +2014,13 @@
       <c r="C47" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D47" s="2">
         <v>4.0999999999999996</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="15">
+      <c r="F47" s="3">
         <v>8</v>
       </c>
     </row>
@@ -2040,13 +2034,13 @@
       <c r="C48" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="D48" s="14">
+      <c r="D48" s="2">
         <v>4.95</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="15">
+      <c r="F48" s="3">
         <v>5</v>
       </c>
     </row>
@@ -2060,13 +2054,13 @@
       <c r="C49" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D49" s="14">
+      <c r="D49" s="2">
         <v>3.46</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F49" s="15">
+      <c r="F49" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2080,13 +2074,13 @@
       <c r="C50" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D50" s="14">
+      <c r="D50" s="2">
         <v>4.04</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F50" s="15">
+      <c r="F50" s="3">
         <v>8</v>
       </c>
     </row>
@@ -2100,13 +2094,13 @@
       <c r="C51" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D51" s="14">
-        <v>3.74</v>
+      <c r="D51" s="2">
+        <v>3.56</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2120,13 +2114,13 @@
       <c r="C52" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="2">
         <v>5.63</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F52" s="15">
+      <c r="F52" s="3">
         <v>2</v>
       </c>
     </row>
@@ -2140,13 +2134,13 @@
       <c r="C53" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D53" s="14">
+      <c r="D53" s="2">
         <v>6.86</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="15">
+      <c r="F53" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2160,13 +2154,13 @@
       <c r="C54" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="D54" s="14">
-        <v>5.45</v>
+      <c r="D54" s="2">
+        <v>6.12</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="15">
+      <c r="F54" s="3">
         <v>1</v>
       </c>
     </row>
@@ -2180,13 +2174,13 @@
       <c r="C55" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D55" s="14">
+      <c r="D55" s="2">
         <v>11.3</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="15">
+      <c r="F55" s="3">
         <v>2</v>
       </c>
     </row>
@@ -2200,14 +2194,14 @@
       <c r="C56" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="D56" s="14">
+      <c r="D56" s="2">
         <v>12.05</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="15">
-        <v>4</v>
+      <c r="F56" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2220,13 +2214,13 @@
       <c r="C57" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D57" s="14">
+      <c r="D57" s="2">
         <v>3.11</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="15">
+      <c r="F57" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2240,13 +2234,13 @@
       <c r="C58" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D58" s="14">
+      <c r="D58" s="2">
         <v>3.04</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="15">
+      <c r="F58" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2260,13 +2254,13 @@
       <c r="C59" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D59" s="14">
+      <c r="D59" s="2">
         <v>3.34</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="15">
+      <c r="F59" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2280,14 +2274,14 @@
       <c r="C60" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D60" s="14">
+      <c r="D60" s="2">
         <v>4.21</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="15">
-        <v>2</v>
+      <c r="F60" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2300,14 +2294,14 @@
       <c r="C61" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D61" s="14">
+      <c r="D61" s="2">
         <v>4.05</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="15">
-        <v>5</v>
+      <c r="F61" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2320,13 +2314,13 @@
       <c r="C62" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D62" s="14">
+      <c r="D62" s="2">
         <v>5.01</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="15">
+      <c r="F62" s="3">
         <v>10</v>
       </c>
     </row>
@@ -2340,13 +2334,13 @@
       <c r="C63" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="D63" s="14">
+      <c r="D63" s="2">
         <v>3.9</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="15">
+      <c r="F63" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2360,13 +2354,13 @@
       <c r="C64" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D64" s="14">
+      <c r="D64" s="2">
         <v>4.04</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="15">
+      <c r="F64" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2380,13 +2374,13 @@
       <c r="C65" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D65" s="14">
+      <c r="D65" s="2">
         <v>4.04</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="15">
+      <c r="F65" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2400,14 +2394,14 @@
       <c r="C66" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D66" s="14">
-        <v>3.86</v>
+      <c r="D66" s="2">
+        <v>4.07</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="15">
-        <v>-4</v>
+      <c r="F66" s="3">
+        <v>-6</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2420,13 +2414,13 @@
       <c r="C67" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D67" s="14">
+      <c r="D67" s="2">
         <v>5.8</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="15">
+      <c r="F67" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2440,13 +2434,13 @@
       <c r="C68" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D68" s="14">
+      <c r="D68" s="2">
         <v>6.86</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="15">
+      <c r="F68" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2460,14 +2454,14 @@
       <c r="C69" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="D69" s="14">
+      <c r="D69" s="2">
         <v>6.2700000000000005</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="F69" s="15">
-        <v>8</v>
+      <c r="F69" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2480,13 +2474,13 @@
       <c r="C70" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="D70" s="14">
+      <c r="D70" s="2">
         <v>12.790000000000001</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F70" s="15">
+      <c r="F70" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2501,13 +2495,13 @@
         <v>189</v>
       </c>
       <c r="D71" s="9">
-        <v>7.6</v>
+        <v>8.19</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>138</v>
       </c>
       <c r="F71" s="13">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/bicones.xlsx
+++ b/prix/bicones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1754BDBF-7091-4BEC-B8E2-B10CE5A58E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D17814D-D6EB-4CAB-85FE-0043BF469DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{CE534A2A-185F-4964-A8EA-80A75C3E7C34}"/>
   </bookViews>
@@ -691,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -729,6 +729,18 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1114,13 +1126,13 @@
       <c r="C2" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="14">
         <v>4.92</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="15">
         <v>19</v>
       </c>
     </row>
@@ -1134,13 +1146,13 @@
       <c r="C3" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="14">
         <v>5.3100000000000005</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1154,13 +1166,13 @@
       <c r="C4" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="14">
         <v>4.8600000000000003</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1174,13 +1186,13 @@
       <c r="C5" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="14">
         <v>4.8899999999999997</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="15">
         <v>5</v>
       </c>
     </row>
@@ -1194,14 +1206,14 @@
       <c r="C6" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="14">
         <v>5.03</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="3">
-        <v>8</v>
+      <c r="F6" s="15">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -1214,13 +1226,13 @@
       <c r="C7" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="14">
         <v>7.82</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="15">
         <v>8</v>
       </c>
     </row>
@@ -1234,13 +1246,13 @@
       <c r="C8" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="14">
         <v>8.17</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="15">
         <v>10</v>
       </c>
     </row>
@@ -1254,13 +1266,13 @@
       <c r="C9" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="14">
         <v>13.1</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="15">
         <v>12</v>
       </c>
     </row>
@@ -1274,13 +1286,13 @@
       <c r="C10" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="14">
         <v>6.49</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1294,13 +1306,13 @@
       <c r="C11" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="14">
         <v>4.8600000000000003</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="15">
         <v>25</v>
       </c>
     </row>
@@ -1314,14 +1326,14 @@
       <c r="C12" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="14">
         <v>6.28</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="3">
-        <v>8</v>
+      <c r="F12" s="15">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1334,13 +1346,13 @@
       <c r="C13" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="14">
         <v>3.11</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="15">
         <v>10</v>
       </c>
     </row>
@@ -1354,13 +1366,13 @@
       <c r="C14" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="14">
         <v>4.62</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1374,14 +1386,14 @@
       <c r="C15" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="14">
         <v>4.62</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="3">
-        <v>12</v>
+      <c r="F15" s="15">
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1394,13 +1406,13 @@
       <c r="C16" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="14">
         <v>13.25</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="15">
         <v>8</v>
       </c>
     </row>
@@ -1414,14 +1426,14 @@
       <c r="C17" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="14">
         <v>5.45</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="3">
-        <v>11</v>
+      <c r="F17" s="15">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1434,13 +1446,13 @@
       <c r="C18" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="14">
         <v>6.3</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="15">
         <v>5</v>
       </c>
     </row>
@@ -1454,13 +1466,13 @@
       <c r="C19" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="14">
         <v>8.25</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="15">
         <v>10</v>
       </c>
     </row>
@@ -1474,13 +1486,13 @@
       <c r="C20" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="14">
         <v>11.700000000000001</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="15">
         <v>5</v>
       </c>
     </row>
@@ -1494,13 +1506,13 @@
       <c r="C21" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="14">
         <v>7.18</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="15">
         <v>5</v>
       </c>
     </row>
@@ -1514,13 +1526,13 @@
       <c r="C22" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="14">
         <v>5.9</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1534,13 +1546,13 @@
       <c r="C23" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="14">
         <v>6.99</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="15">
         <v>6</v>
       </c>
     </row>
@@ -1554,13 +1566,13 @@
       <c r="C24" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="14">
         <v>7.68</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="15">
         <v>2</v>
       </c>
     </row>
@@ -1574,14 +1586,14 @@
       <c r="C25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="14">
         <v>7.7700000000000005</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="3">
-        <v>1</v>
+      <c r="F25" s="15">
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1594,13 +1606,13 @@
       <c r="C26" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="14">
         <v>12.5</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1614,14 +1626,14 @@
       <c r="C27" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="14">
         <v>13.700000000000001</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="3">
-        <v>17</v>
+      <c r="F27" s="15">
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1634,13 +1646,13 @@
       <c r="C28" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="14">
         <v>24.27</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1654,13 +1666,13 @@
       <c r="C29" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="14">
         <v>9.0500000000000007</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="15">
         <v>15</v>
       </c>
     </row>
@@ -1674,13 +1686,13 @@
       <c r="C30" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="14">
         <v>6.63</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1694,13 +1706,13 @@
       <c r="C31" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="14">
         <v>4.16</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1714,13 +1726,13 @@
       <c r="C32" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="14">
         <v>5.01</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1734,13 +1746,13 @@
       <c r="C33" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="14">
         <v>6.3500000000000005</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="15">
         <v>12</v>
       </c>
     </row>
@@ -1754,13 +1766,13 @@
       <c r="C34" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="14">
         <v>7.3500000000000005</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="15">
         <v>9</v>
       </c>
     </row>
@@ -1774,13 +1786,13 @@
       <c r="C35" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="14">
         <v>6.12</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1794,13 +1806,13 @@
       <c r="C36" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="14">
         <v>6.36</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="15">
         <v>9</v>
       </c>
     </row>
@@ -1814,13 +1826,13 @@
       <c r="C37" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="14">
         <v>4.62</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="15">
         <v>14</v>
       </c>
     </row>
@@ -1834,14 +1846,14 @@
       <c r="C38" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="14">
         <v>5.4</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="3">
-        <v>7</v>
+      <c r="F38" s="15">
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1854,13 +1866,13 @@
       <c r="C39" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="14">
         <v>6.12</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1874,13 +1886,13 @@
       <c r="C40" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="14">
         <v>6.12</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1894,13 +1906,13 @@
       <c r="C41" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="14">
         <v>10.07</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="15">
         <v>25</v>
       </c>
     </row>
@@ -1914,13 +1926,13 @@
       <c r="C42" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="14">
         <v>4.6000000000000005</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1934,13 +1946,13 @@
       <c r="C43" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="14">
         <v>3.94</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1954,13 +1966,13 @@
       <c r="C44" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="14">
         <v>4.28</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1974,13 +1986,13 @@
       <c r="C45" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="14">
         <v>4.6000000000000005</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1994,13 +2006,13 @@
       <c r="C46" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="14">
         <v>5.3</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2014,13 +2026,13 @@
       <c r="C47" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="15">
         <v>8</v>
       </c>
     </row>
@@ -2034,13 +2046,13 @@
       <c r="C48" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="14">
         <v>4.95</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="15">
         <v>5</v>
       </c>
     </row>
@@ -2054,13 +2066,13 @@
       <c r="C49" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="14">
         <v>3.46</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2074,13 +2086,13 @@
       <c r="C50" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="14">
         <v>4.04</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="15">
         <v>8</v>
       </c>
     </row>
@@ -2094,14 +2106,14 @@
       <c r="C51" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="14">
         <v>3.56</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="3">
-        <v>0</v>
+      <c r="F51" s="15">
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2114,13 +2126,13 @@
       <c r="C52" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="14">
         <v>5.63</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="15">
         <v>2</v>
       </c>
     </row>
@@ -2134,13 +2146,13 @@
       <c r="C53" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="14">
         <v>6.86</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2154,14 +2166,14 @@
       <c r="C54" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="14">
         <v>6.12</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="3">
-        <v>1</v>
+      <c r="F54" s="15">
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2174,13 +2186,13 @@
       <c r="C55" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="14">
         <v>11.3</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="15">
         <v>2</v>
       </c>
     </row>
@@ -2194,14 +2206,14 @@
       <c r="C56" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="14">
         <v>12.05</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="3">
-        <v>3</v>
+      <c r="F56" s="15">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2214,13 +2226,13 @@
       <c r="C57" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="14">
         <v>3.11</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2234,13 +2246,13 @@
       <c r="C58" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="14">
         <v>3.04</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2254,13 +2266,13 @@
       <c r="C59" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="14">
         <v>3.34</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2274,13 +2286,13 @@
       <c r="C60" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="14">
         <v>4.21</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2294,13 +2306,13 @@
       <c r="C61" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="14">
         <v>4.05</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61" s="15">
         <v>4</v>
       </c>
     </row>
@@ -2314,13 +2326,13 @@
       <c r="C62" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="14">
         <v>5.01</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="15">
         <v>10</v>
       </c>
     </row>
@@ -2334,13 +2346,13 @@
       <c r="C63" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="14">
         <v>3.9</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2354,13 +2366,13 @@
       <c r="C64" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="14">
         <v>4.04</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F64" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2374,13 +2386,13 @@
       <c r="C65" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="14">
         <v>4.04</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2394,14 +2406,14 @@
       <c r="C66" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="14">
         <v>4.07</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="3">
-        <v>-6</v>
+      <c r="F66" s="15">
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2414,13 +2426,13 @@
       <c r="C67" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="14">
         <v>5.8</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2434,13 +2446,13 @@
       <c r="C68" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="14">
         <v>6.86</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2454,14 +2466,14 @@
       <c r="C69" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="14">
         <v>6.2700000000000005</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="F69" s="3">
-        <v>6</v>
+      <c r="F69" s="15">
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2474,13 +2486,13 @@
       <c r="C70" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="14">
         <v>12.790000000000001</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2494,14 +2506,14 @@
       <c r="C71" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D71" s="9">
-        <v>8.19</v>
+      <c r="D71" s="16">
+        <v>9.43</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="F71" s="13">
-        <v>23</v>
+      <c r="F71" s="17">
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -2514,13 +2526,13 @@
       <c r="C72" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="16">
         <v>6.03</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F72" s="13">
+      <c r="F72" s="17">
         <v>26</v>
       </c>
     </row>

--- a/prix/bicones.xlsx
+++ b/prix/bicones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D17814D-D6EB-4CAB-85FE-0043BF469DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57824853-6395-40C8-AC3B-F5C9C97699D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{CE534A2A-185F-4964-A8EA-80A75C3E7C34}"/>
   </bookViews>
@@ -691,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -729,12 +729,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1167,13 +1161,13 @@
         <v>157</v>
       </c>
       <c r="D4" s="14">
-        <v>4.8600000000000003</v>
+        <v>3.34</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -1213,7 +1207,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="15">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -1253,7 +1247,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -1273,7 +1267,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -1393,7 +1387,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1433,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1553,7 +1547,7 @@
         <v>42</v>
       </c>
       <c r="F23" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1673,7 +1667,7 @@
         <v>54</v>
       </c>
       <c r="F29" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1773,7 +1767,7 @@
         <v>64</v>
       </c>
       <c r="F34" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1813,7 +1807,7 @@
         <v>68</v>
       </c>
       <c r="F36" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1853,7 +1847,7 @@
         <v>72</v>
       </c>
       <c r="F38" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2013,7 +2007,7 @@
         <v>88</v>
       </c>
       <c r="F46" s="15">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2113,7 +2107,7 @@
         <v>98</v>
       </c>
       <c r="F51" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2213,7 +2207,7 @@
         <v>108</v>
       </c>
       <c r="F56" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2313,7 +2307,7 @@
         <v>118</v>
       </c>
       <c r="F61" s="15">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2413,7 +2407,7 @@
         <v>128</v>
       </c>
       <c r="F66" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2473,7 +2467,7 @@
         <v>134</v>
       </c>
       <c r="F69" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2506,13 +2500,13 @@
       <c r="C71" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D71" s="16">
+      <c r="D71" s="2">
         <v>9.43</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="F71" s="17">
+      <c r="F71" s="3">
         <v>26</v>
       </c>
     </row>
@@ -2526,13 +2520,13 @@
       <c r="C72" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D72" s="16">
+      <c r="D72" s="2">
         <v>6.03</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F72" s="17">
+      <c r="F72" s="3">
         <v>26</v>
       </c>
     </row>

--- a/prix/bicones.xlsx
+++ b/prix/bicones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57824853-6395-40C8-AC3B-F5C9C97699D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F7D7E6-F4AC-4E33-9436-08BA1AD874CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{CE534A2A-185F-4964-A8EA-80A75C3E7C34}"/>
   </bookViews>
@@ -691,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -731,9 +731,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1126,7 +1123,7 @@
       <c r="E2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="3">
         <v>19</v>
       </c>
     </row>
@@ -1146,7 +1143,7 @@
       <c r="E3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1166,7 +1163,7 @@
       <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
     </row>
@@ -1186,7 +1183,7 @@
       <c r="E5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1206,7 +1203,7 @@
       <c r="E6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="3">
         <v>12</v>
       </c>
     </row>
@@ -1226,7 +1223,7 @@
       <c r="E7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="3">
         <v>8</v>
       </c>
     </row>
@@ -1246,7 +1243,7 @@
       <c r="E8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="3">
         <v>9</v>
       </c>
     </row>
@@ -1266,7 +1263,7 @@
       <c r="E9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="3">
         <v>11</v>
       </c>
     </row>
@@ -1286,7 +1283,7 @@
       <c r="E10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1306,7 +1303,7 @@
       <c r="E11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="3">
         <v>25</v>
       </c>
     </row>
@@ -1326,7 +1323,7 @@
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="3">
         <v>7</v>
       </c>
     </row>
@@ -1346,7 +1343,7 @@
       <c r="E13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="3">
         <v>10</v>
       </c>
     </row>
@@ -1366,7 +1363,7 @@
       <c r="E14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1386,7 +1383,7 @@
       <c r="E15" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="3">
         <v>10</v>
       </c>
     </row>
@@ -1406,7 +1403,7 @@
       <c r="E16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="3">
         <v>8</v>
       </c>
     </row>
@@ -1426,7 +1423,7 @@
       <c r="E17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="3">
         <v>7</v>
       </c>
     </row>
@@ -1446,7 +1443,7 @@
       <c r="E18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1466,7 +1463,7 @@
       <c r="E19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="3">
         <v>10</v>
       </c>
     </row>
@@ -1486,7 +1483,7 @@
       <c r="E20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1506,7 +1503,7 @@
       <c r="E21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1526,7 +1523,7 @@
       <c r="E22" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1546,7 +1543,7 @@
       <c r="E23" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1566,7 +1563,7 @@
       <c r="E24" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="3">
         <v>2</v>
       </c>
     </row>
@@ -1586,7 +1583,7 @@
       <c r="E25" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="3">
         <v>11</v>
       </c>
     </row>
@@ -1606,7 +1603,7 @@
       <c r="E26" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1626,7 +1623,7 @@
       <c r="E27" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="3">
         <v>22</v>
       </c>
     </row>
@@ -1646,7 +1643,7 @@
       <c r="E28" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1666,7 +1663,7 @@
       <c r="E29" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="3">
         <v>14</v>
       </c>
     </row>
@@ -1686,7 +1683,7 @@
       <c r="E30" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1706,7 +1703,7 @@
       <c r="E31" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1726,7 +1723,7 @@
       <c r="E32" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1746,7 +1743,7 @@
       <c r="E33" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="3">
         <v>12</v>
       </c>
     </row>
@@ -1766,7 +1763,7 @@
       <c r="E34" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="3">
         <v>7</v>
       </c>
     </row>
@@ -1786,7 +1783,7 @@
       <c r="E35" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1806,7 +1803,7 @@
       <c r="E36" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="3">
         <v>8</v>
       </c>
     </row>
@@ -1826,7 +1823,7 @@
       <c r="E37" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="3">
         <v>14</v>
       </c>
     </row>
@@ -1846,7 +1843,7 @@
       <c r="E38" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="15">
+      <c r="F38" s="3">
         <v>3</v>
       </c>
     </row>
@@ -1866,7 +1863,7 @@
       <c r="E39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1886,7 +1883,7 @@
       <c r="E40" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1906,7 +1903,7 @@
       <c r="E41" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="3">
         <v>25</v>
       </c>
     </row>
@@ -1926,7 +1923,7 @@
       <c r="E42" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1946,7 +1943,7 @@
       <c r="E43" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1966,7 +1963,7 @@
       <c r="E44" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F44" s="15">
+      <c r="F44" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1986,7 +1983,7 @@
       <c r="E45" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="15">
+      <c r="F45" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2006,7 +2003,7 @@
       <c r="E46" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="15">
+      <c r="F46" s="3">
         <v>-3</v>
       </c>
     </row>
@@ -2026,7 +2023,7 @@
       <c r="E47" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="15">
+      <c r="F47" s="3">
         <v>8</v>
       </c>
     </row>
@@ -2046,7 +2043,7 @@
       <c r="E48" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="15">
+      <c r="F48" s="3">
         <v>5</v>
       </c>
     </row>
@@ -2066,7 +2063,7 @@
       <c r="E49" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F49" s="15">
+      <c r="F49" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2086,7 +2083,7 @@
       <c r="E50" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F50" s="15">
+      <c r="F50" s="3">
         <v>8</v>
       </c>
     </row>
@@ -2106,7 +2103,7 @@
       <c r="E51" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="3">
         <v>10</v>
       </c>
     </row>
@@ -2126,7 +2123,7 @@
       <c r="E52" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F52" s="15">
+      <c r="F52" s="3">
         <v>2</v>
       </c>
     </row>
@@ -2146,7 +2143,7 @@
       <c r="E53" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="15">
+      <c r="F53" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2166,7 +2163,7 @@
       <c r="E54" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="15">
+      <c r="F54" s="3">
         <v>18</v>
       </c>
     </row>
@@ -2186,7 +2183,7 @@
       <c r="E55" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="15">
+      <c r="F55" s="3">
         <v>2</v>
       </c>
     </row>
@@ -2206,7 +2203,7 @@
       <c r="E56" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="15">
+      <c r="F56" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2226,7 +2223,7 @@
       <c r="E57" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="15">
+      <c r="F57" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2246,7 +2243,7 @@
       <c r="E58" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="15">
+      <c r="F58" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2266,7 +2263,7 @@
       <c r="E59" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="15">
+      <c r="F59" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2286,7 +2283,7 @@
       <c r="E60" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="15">
+      <c r="F60" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2306,7 +2303,7 @@
       <c r="E61" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="15">
+      <c r="F61" s="3">
         <v>14</v>
       </c>
     </row>
@@ -2326,7 +2323,7 @@
       <c r="E62" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="15">
+      <c r="F62" s="3">
         <v>10</v>
       </c>
     </row>
@@ -2346,7 +2343,7 @@
       <c r="E63" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="15">
+      <c r="F63" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2366,7 +2363,7 @@
       <c r="E64" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="15">
+      <c r="F64" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2386,7 +2383,7 @@
       <c r="E65" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="15">
+      <c r="F65" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2406,7 +2403,7 @@
       <c r="E66" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="15">
+      <c r="F66" s="3">
         <v>5</v>
       </c>
     </row>
@@ -2426,7 +2423,7 @@
       <c r="E67" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="15">
+      <c r="F67" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2446,7 +2443,7 @@
       <c r="E68" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="15">
+      <c r="F68" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2466,7 +2463,7 @@
       <c r="E69" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="F69" s="15">
+      <c r="F69" s="3">
         <v>3</v>
       </c>
     </row>
@@ -2486,7 +2483,7 @@
       <c r="E70" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F70" s="15">
+      <c r="F70" s="3">
         <v>0</v>
       </c>
     </row>

--- a/prix/bicones.xlsx
+++ b/prix/bicones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F7D7E6-F4AC-4E33-9436-08BA1AD874CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145416DD-8EDD-4EB0-98C6-99348569C161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{CE534A2A-185F-4964-A8EA-80A75C3E7C34}"/>
   </bookViews>
@@ -691,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -731,6 +731,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1123,7 +1126,7 @@
       <c r="E2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="15">
         <v>19</v>
       </c>
     </row>
@@ -1143,7 +1146,7 @@
       <c r="E3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1163,8 +1166,8 @@
       <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="3">
-        <v>10</v>
+      <c r="F4" s="15">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,8 +1186,8 @@
       <c r="E5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="3">
-        <v>5</v>
+      <c r="F5" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -1203,7 +1206,7 @@
       <c r="E6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="15">
         <v>12</v>
       </c>
     </row>
@@ -1223,7 +1226,7 @@
       <c r="E7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="15">
         <v>8</v>
       </c>
     </row>
@@ -1243,7 +1246,7 @@
       <c r="E8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="15">
         <v>9</v>
       </c>
     </row>
@@ -1263,7 +1266,7 @@
       <c r="E9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="15">
         <v>11</v>
       </c>
     </row>
@@ -1283,7 +1286,7 @@
       <c r="E10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1303,7 +1306,7 @@
       <c r="E11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="15">
         <v>25</v>
       </c>
     </row>
@@ -1323,8 +1326,8 @@
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="3">
-        <v>7</v>
+      <c r="F12" s="15">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1343,7 +1346,7 @@
       <c r="E13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="15">
         <v>10</v>
       </c>
     </row>
@@ -1363,7 +1366,7 @@
       <c r="E14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1383,7 +1386,7 @@
       <c r="E15" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="15">
         <v>10</v>
       </c>
     </row>
@@ -1403,8 +1406,8 @@
       <c r="E16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="3">
-        <v>8</v>
+      <c r="F16" s="15">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1423,7 +1426,7 @@
       <c r="E17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="15">
         <v>7</v>
       </c>
     </row>
@@ -1443,7 +1446,7 @@
       <c r="E18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="15">
         <v>5</v>
       </c>
     </row>
@@ -1463,7 +1466,7 @@
       <c r="E19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="15">
         <v>10</v>
       </c>
     </row>
@@ -1483,7 +1486,7 @@
       <c r="E20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="15">
         <v>5</v>
       </c>
     </row>
@@ -1503,7 +1506,7 @@
       <c r="E21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="15">
         <v>5</v>
       </c>
     </row>
@@ -1523,7 +1526,7 @@
       <c r="E22" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1543,7 +1546,7 @@
       <c r="E23" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="15">
         <v>5</v>
       </c>
     </row>
@@ -1563,8 +1566,8 @@
       <c r="E24" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="3">
-        <v>2</v>
+      <c r="F24" s="15">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1583,8 +1586,8 @@
       <c r="E25" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="3">
-        <v>11</v>
+      <c r="F25" s="15">
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1603,7 +1606,7 @@
       <c r="E26" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1623,7 +1626,7 @@
       <c r="E27" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="15">
         <v>22</v>
       </c>
     </row>
@@ -1643,7 +1646,7 @@
       <c r="E28" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1663,7 +1666,7 @@
       <c r="E29" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="15">
         <v>14</v>
       </c>
     </row>
@@ -1683,7 +1686,7 @@
       <c r="E30" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1703,7 +1706,7 @@
       <c r="E31" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1723,7 +1726,7 @@
       <c r="E32" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1743,8 +1746,8 @@
       <c r="E33" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="3">
-        <v>12</v>
+      <c r="F33" s="15">
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1758,12 +1761,12 @@
         <v>171</v>
       </c>
       <c r="D34" s="14">
-        <v>7.3500000000000005</v>
+        <v>6.97</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="15">
         <v>7</v>
       </c>
     </row>
@@ -1783,7 +1786,7 @@
       <c r="E35" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1803,7 +1806,7 @@
       <c r="E36" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="15">
         <v>8</v>
       </c>
     </row>
@@ -1823,7 +1826,7 @@
       <c r="E37" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="15">
         <v>14</v>
       </c>
     </row>
@@ -1843,8 +1846,8 @@
       <c r="E38" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="3">
-        <v>3</v>
+      <c r="F38" s="15">
+        <v>-3</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1863,7 +1866,7 @@
       <c r="E39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1883,7 +1886,7 @@
       <c r="E40" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1903,7 +1906,7 @@
       <c r="E41" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="15">
         <v>25</v>
       </c>
     </row>
@@ -1923,7 +1926,7 @@
       <c r="E42" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1943,7 +1946,7 @@
       <c r="E43" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1963,7 +1966,7 @@
       <c r="E44" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1983,7 +1986,7 @@
       <c r="E45" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2003,8 +2006,8 @@
       <c r="E46" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="3">
-        <v>-3</v>
+      <c r="F46" s="15">
+        <v>-5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2023,8 +2026,8 @@
       <c r="E47" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="3">
-        <v>8</v>
+      <c r="F47" s="15">
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2043,7 +2046,7 @@
       <c r="E48" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="15">
         <v>5</v>
       </c>
     </row>
@@ -2063,7 +2066,7 @@
       <c r="E49" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2083,7 +2086,7 @@
       <c r="E50" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="15">
         <v>8</v>
       </c>
     </row>
@@ -2103,8 +2106,8 @@
       <c r="E51" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="3">
-        <v>10</v>
+      <c r="F51" s="15">
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2123,7 +2126,7 @@
       <c r="E52" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="15">
         <v>2</v>
       </c>
     </row>
@@ -2143,7 +2146,7 @@
       <c r="E53" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2163,8 +2166,8 @@
       <c r="E54" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="3">
-        <v>18</v>
+      <c r="F54" s="15">
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2183,7 +2186,7 @@
       <c r="E55" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="15">
         <v>2</v>
       </c>
     </row>
@@ -2203,7 +2206,7 @@
       <c r="E56" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2223,7 +2226,7 @@
       <c r="E57" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2243,7 +2246,7 @@
       <c r="E58" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2263,7 +2266,7 @@
       <c r="E59" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2283,7 +2286,7 @@
       <c r="E60" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2303,8 +2306,8 @@
       <c r="E61" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="3">
-        <v>14</v>
+      <c r="F61" s="15">
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2323,7 +2326,7 @@
       <c r="E62" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="15">
         <v>10</v>
       </c>
     </row>
@@ -2343,7 +2346,7 @@
       <c r="E63" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2363,7 +2366,7 @@
       <c r="E64" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F64" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2383,7 +2386,7 @@
       <c r="E65" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2403,8 +2406,8 @@
       <c r="E66" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="3">
-        <v>5</v>
+      <c r="F66" s="15">
+        <v>-6</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2423,7 +2426,7 @@
       <c r="E67" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2443,7 +2446,7 @@
       <c r="E68" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2463,8 +2466,8 @@
       <c r="E69" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="F69" s="3">
-        <v>3</v>
+      <c r="F69" s="15">
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2483,7 +2486,7 @@
       <c r="E70" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2524,7 +2527,7 @@
         <v>140</v>
       </c>
       <c r="F72" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
